--- a/2026夏AGS_ガントチャート.xlsx
+++ b/2026夏AGS_ガントチャート.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB3E70EF-9D0D-4F29-B87E-B99D9A116535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01BB737B-424F-40D2-BD84-A19DB46AF035}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="51">
   <si>
     <t>企画制作　進捗管理表</t>
     <phoneticPr fontId="19"/>
@@ -359,6 +359,72 @@
     </rPh>
     <rPh sb="13" eb="14">
       <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>プレイヤー</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>シーン遷移</t>
+    <rPh sb="3" eb="5">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>マップ</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>オンラインプレイ</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>ミニゲーム</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>当たり判定</t>
+    <rPh sb="0" eb="1">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ハンテイ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>鬼ごっこ</t>
+    <rPh sb="0" eb="1">
+      <t>オニ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>チャンバラ</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>描画処理</t>
+    <rPh sb="0" eb="4">
+      <t>ビョウガショリ</t>
+    </rPh>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>タイトル</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>ゲーム</t>
+    <phoneticPr fontId="19"/>
+  </si>
+  <si>
+    <t>ゲーム終了</t>
+    <rPh sb="3" eb="5">
+      <t>シュウリョウ</t>
     </rPh>
     <phoneticPr fontId="19"/>
   </si>
@@ -1477,12 +1543,21 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="183" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="20" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -1503,15 +1578,6 @@
     </xf>
     <xf numFmtId="183" fontId="24" fillId="0" borderId="0" xfId="9" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="183" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2142,22 +2208,22 @@
       <c r="D1" s="82" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="108">
+      <c r="E1" s="112">
         <v>45761</v>
       </c>
-      <c r="F1" s="108"/>
-      <c r="G1" s="108"/>
+      <c r="F1" s="112"/>
+      <c r="G1" s="112"/>
     </row>
     <row r="2" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A2" s="110" t="s">
+      <c r="A2" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="110"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="110"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
       <c r="H2" s="99"/>
       <c r="I2" s="99"/>
       <c r="J2" s="99"/>
@@ -2165,15 +2231,15 @@
       <c r="L2" s="99"/>
     </row>
     <row r="3" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A3" s="110" t="s">
+      <c r="A3" s="113" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="110"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="110"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="110"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="113"/>
       <c r="H3" s="99"/>
       <c r="I3" s="99"/>
       <c r="J3" s="99"/>
@@ -2181,15 +2247,15 @@
       <c r="L3" s="99"/>
     </row>
     <row r="4" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A4" s="110" t="s">
+      <c r="A4" s="113" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="110"/>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
       <c r="H4" s="99"/>
       <c r="I4" s="99"/>
       <c r="J4" s="99"/>
@@ -2197,168 +2263,168 @@
       <c r="L4" s="99"/>
     </row>
     <row r="5" spans="1:92" ht="15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D5" s="114"/>
-      <c r="E5" s="114"/>
-      <c r="F5" s="115"/>
-      <c r="G5" s="115"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="118"/>
     </row>
     <row r="6" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A6" s="80"/>
-      <c r="B6" s="116"/>
-      <c r="C6" s="116"/>
-      <c r="D6" s="111"/>
-      <c r="E6" s="111"/>
-      <c r="F6" s="112"/>
-      <c r="G6" s="113"/>
-      <c r="H6" s="109">
+      <c r="B6" s="119"/>
+      <c r="C6" s="119"/>
+      <c r="D6" s="114"/>
+      <c r="E6" s="114"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="116"/>
+      <c r="H6" s="108">
         <f>H7</f>
         <v>45761</v>
       </c>
-      <c r="I6" s="109"/>
-      <c r="J6" s="109"/>
-      <c r="K6" s="109"/>
-      <c r="L6" s="109"/>
-      <c r="M6" s="109">
+      <c r="I6" s="108"/>
+      <c r="J6" s="108"/>
+      <c r="K6" s="108"/>
+      <c r="L6" s="108"/>
+      <c r="M6" s="108">
         <f>H6+7</f>
         <v>45768</v>
       </c>
-      <c r="N6" s="109"/>
-      <c r="O6" s="109"/>
-      <c r="P6" s="109"/>
-      <c r="Q6" s="109"/>
-      <c r="R6" s="109">
+      <c r="N6" s="108"/>
+      <c r="O6" s="108"/>
+      <c r="P6" s="108"/>
+      <c r="Q6" s="108"/>
+      <c r="R6" s="108">
         <f>M6+7</f>
         <v>45775</v>
       </c>
-      <c r="S6" s="109"/>
-      <c r="T6" s="109"/>
-      <c r="U6" s="109"/>
-      <c r="V6" s="109"/>
-      <c r="W6" s="109">
+      <c r="S6" s="108"/>
+      <c r="T6" s="108"/>
+      <c r="U6" s="108"/>
+      <c r="V6" s="108"/>
+      <c r="W6" s="108">
         <f>R6+7</f>
         <v>45782</v>
       </c>
-      <c r="X6" s="109"/>
-      <c r="Y6" s="109"/>
-      <c r="Z6" s="109"/>
-      <c r="AA6" s="109"/>
-      <c r="AB6" s="109">
+      <c r="X6" s="108"/>
+      <c r="Y6" s="108"/>
+      <c r="Z6" s="108"/>
+      <c r="AA6" s="108"/>
+      <c r="AB6" s="108">
         <f>W6+7</f>
         <v>45789</v>
       </c>
-      <c r="AC6" s="109"/>
-      <c r="AD6" s="109"/>
-      <c r="AE6" s="109"/>
-      <c r="AF6" s="109"/>
-      <c r="AG6" s="109">
+      <c r="AC6" s="108"/>
+      <c r="AD6" s="108"/>
+      <c r="AE6" s="108"/>
+      <c r="AF6" s="108"/>
+      <c r="AG6" s="108">
         <f>AB6+7</f>
         <v>45796</v>
       </c>
-      <c r="AH6" s="109"/>
-      <c r="AI6" s="109"/>
-      <c r="AJ6" s="109"/>
-      <c r="AK6" s="109"/>
-      <c r="AL6" s="109">
+      <c r="AH6" s="108"/>
+      <c r="AI6" s="108"/>
+      <c r="AJ6" s="108"/>
+      <c r="AK6" s="108"/>
+      <c r="AL6" s="108">
         <f>AG6+7</f>
         <v>45803</v>
       </c>
-      <c r="AM6" s="109"/>
-      <c r="AN6" s="109"/>
-      <c r="AO6" s="109"/>
-      <c r="AP6" s="109"/>
-      <c r="AQ6" s="109">
+      <c r="AM6" s="108"/>
+      <c r="AN6" s="108"/>
+      <c r="AO6" s="108"/>
+      <c r="AP6" s="108"/>
+      <c r="AQ6" s="108">
         <f>AL6+7</f>
         <v>45810</v>
       </c>
-      <c r="AR6" s="109"/>
-      <c r="AS6" s="109"/>
-      <c r="AT6" s="109"/>
-      <c r="AU6" s="109"/>
-      <c r="AV6" s="109">
+      <c r="AR6" s="108"/>
+      <c r="AS6" s="108"/>
+      <c r="AT6" s="108"/>
+      <c r="AU6" s="108"/>
+      <c r="AV6" s="108">
         <f>AQ6+7</f>
         <v>45817</v>
       </c>
-      <c r="AW6" s="109"/>
-      <c r="AX6" s="109"/>
-      <c r="AY6" s="109"/>
-      <c r="AZ6" s="109"/>
-      <c r="BA6" s="109">
+      <c r="AW6" s="108"/>
+      <c r="AX6" s="108"/>
+      <c r="AY6" s="108"/>
+      <c r="AZ6" s="108"/>
+      <c r="BA6" s="108">
         <f>AV6+7</f>
         <v>45824</v>
       </c>
-      <c r="BB6" s="109"/>
-      <c r="BC6" s="109"/>
-      <c r="BD6" s="109"/>
-      <c r="BE6" s="109"/>
-      <c r="BF6" s="109">
+      <c r="BB6" s="108"/>
+      <c r="BC6" s="108"/>
+      <c r="BD6" s="108"/>
+      <c r="BE6" s="108"/>
+      <c r="BF6" s="108">
         <f>BA6+7</f>
         <v>45831</v>
       </c>
-      <c r="BG6" s="109"/>
-      <c r="BH6" s="109"/>
-      <c r="BI6" s="109"/>
-      <c r="BJ6" s="109"/>
-      <c r="BK6" s="109">
+      <c r="BG6" s="108"/>
+      <c r="BH6" s="108"/>
+      <c r="BI6" s="108"/>
+      <c r="BJ6" s="108"/>
+      <c r="BK6" s="108">
         <f>BF6+7</f>
         <v>45838</v>
       </c>
-      <c r="BL6" s="109"/>
-      <c r="BM6" s="109"/>
-      <c r="BN6" s="109"/>
-      <c r="BO6" s="109"/>
-      <c r="BP6" s="109">
+      <c r="BL6" s="108"/>
+      <c r="BM6" s="108"/>
+      <c r="BN6" s="108"/>
+      <c r="BO6" s="108"/>
+      <c r="BP6" s="108">
         <f>BK6+7</f>
         <v>45845</v>
       </c>
-      <c r="BQ6" s="109"/>
-      <c r="BR6" s="109"/>
-      <c r="BS6" s="109"/>
-      <c r="BT6" s="109"/>
-      <c r="BU6" s="109">
+      <c r="BQ6" s="108"/>
+      <c r="BR6" s="108"/>
+      <c r="BS6" s="108"/>
+      <c r="BT6" s="108"/>
+      <c r="BU6" s="108">
         <f>BP6+7</f>
         <v>45852</v>
       </c>
-      <c r="BV6" s="109"/>
-      <c r="BW6" s="109"/>
-      <c r="BX6" s="109"/>
-      <c r="BY6" s="109"/>
-      <c r="BZ6" s="109">
+      <c r="BV6" s="108"/>
+      <c r="BW6" s="108"/>
+      <c r="BX6" s="108"/>
+      <c r="BY6" s="108"/>
+      <c r="BZ6" s="108">
         <f>BU6+7</f>
         <v>45859</v>
       </c>
-      <c r="CA6" s="109"/>
-      <c r="CB6" s="109"/>
-      <c r="CC6" s="109"/>
-      <c r="CD6" s="109"/>
-      <c r="CE6" s="109">
+      <c r="CA6" s="108"/>
+      <c r="CB6" s="108"/>
+      <c r="CC6" s="108"/>
+      <c r="CD6" s="108"/>
+      <c r="CE6" s="108">
         <f>BZ6+7</f>
         <v>45866</v>
       </c>
-      <c r="CF6" s="109"/>
-      <c r="CG6" s="109"/>
-      <c r="CH6" s="109"/>
-      <c r="CI6" s="109"/>
-      <c r="CJ6" s="109">
+      <c r="CF6" s="108"/>
+      <c r="CG6" s="108"/>
+      <c r="CH6" s="108"/>
+      <c r="CI6" s="108"/>
+      <c r="CJ6" s="108">
         <f>CE6+7</f>
         <v>45873</v>
       </c>
-      <c r="CK6" s="109"/>
-      <c r="CL6" s="109"/>
-      <c r="CM6" s="109"/>
-      <c r="CN6" s="109"/>
+      <c r="CK6" s="108"/>
+      <c r="CL6" s="108"/>
+      <c r="CM6" s="108"/>
+      <c r="CN6" s="108"/>
     </row>
     <row r="7" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A7" s="75"/>
       <c r="B7" s="75"/>
       <c r="C7" s="76"/>
-      <c r="D7" s="117" t="s">
+      <c r="D7" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="118"/>
-      <c r="F7" s="119" t="s">
+      <c r="E7" s="110"/>
+      <c r="F7" s="111" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="118"/>
+      <c r="G7" s="110"/>
       <c r="H7" s="77">
         <f>E1-WEEKDAY(E1,1)+2</f>
         <v>45761</v>
@@ -2979,7 +3045,9 @@
       </c>
     </row>
     <row r="9" spans="1:92" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="16"/>
+      <c r="A9" s="16" t="s">
+        <v>39</v>
+      </c>
       <c r="B9" s="17"/>
       <c r="C9" s="18"/>
       <c r="D9" s="19"/>
@@ -3073,7 +3141,9 @@
       <c r="CN9" s="22"/>
     </row>
     <row r="10" spans="1:92" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="71"/>
+      <c r="A10" s="71" t="s">
+        <v>44</v>
+      </c>
       <c r="B10" s="23"/>
       <c r="C10" s="104"/>
       <c r="D10" s="25"/>
@@ -3167,7 +3237,9 @@
       <c r="CN10" s="28"/>
     </row>
     <row r="11" spans="1:92" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A11" s="71"/>
+      <c r="A11" s="71" t="s">
+        <v>47</v>
+      </c>
       <c r="B11" s="23"/>
       <c r="C11" s="104"/>
       <c r="D11" s="25"/>
@@ -3543,7 +3615,9 @@
       <c r="CN14" s="28"/>
     </row>
     <row r="15" spans="1:92" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="29"/>
+      <c r="A15" s="29" t="s">
+        <v>40</v>
+      </c>
       <c r="B15" s="30"/>
       <c r="C15" s="31"/>
       <c r="D15" s="32"/>
@@ -3637,7 +3711,9 @@
       <c r="CN15" s="35"/>
     </row>
     <row r="16" spans="1:92" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="72"/>
+      <c r="A16" s="72" t="s">
+        <v>48</v>
+      </c>
       <c r="B16" s="36"/>
       <c r="C16" s="106"/>
       <c r="D16" s="38"/>
@@ -3731,7 +3807,9 @@
       <c r="CN16" s="41"/>
     </row>
     <row r="17" spans="1:92" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="72"/>
+      <c r="A17" s="72" t="s">
+        <v>49</v>
+      </c>
       <c r="B17" s="36"/>
       <c r="C17" s="106"/>
       <c r="D17" s="38"/>
@@ -3825,7 +3903,9 @@
       <c r="CN17" s="41"/>
     </row>
     <row r="18" spans="1:92" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="72"/>
+      <c r="A18" s="72" t="s">
+        <v>50</v>
+      </c>
       <c r="B18" s="36"/>
       <c r="C18" s="106"/>
       <c r="D18" s="38"/>
@@ -4483,7 +4563,9 @@
       <c r="CN24" s="41"/>
     </row>
     <row r="25" spans="1:92" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="42"/>
+      <c r="A25" s="42" t="s">
+        <v>42</v>
+      </c>
       <c r="B25" s="43"/>
       <c r="C25" s="44"/>
       <c r="D25" s="45"/>
@@ -5235,7 +5317,9 @@
       <c r="CN32" s="54"/>
     </row>
     <row r="33" spans="1:92" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="55"/>
+      <c r="A33" s="55" t="s">
+        <v>43</v>
+      </c>
       <c r="B33" s="56"/>
       <c r="C33" s="57"/>
       <c r="D33" s="58"/>
@@ -5329,7 +5413,9 @@
       <c r="CN33" s="61"/>
     </row>
     <row r="34" spans="1:92" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A34" s="63"/>
+      <c r="A34" s="63" t="s">
+        <v>45</v>
+      </c>
       <c r="B34" s="63"/>
       <c r="C34" s="105"/>
       <c r="D34" s="64"/>
@@ -5423,7 +5509,9 @@
       <c r="CN34" s="67"/>
     </row>
     <row r="35" spans="1:92" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A35" s="74"/>
+      <c r="A35" s="63" t="s">
+        <v>46</v>
+      </c>
       <c r="B35" s="62"/>
       <c r="C35" s="105"/>
       <c r="D35" s="64"/>
@@ -5799,7 +5887,9 @@
       <c r="CN38" s="67"/>
     </row>
     <row r="39" spans="1:92" ht="24" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A39" s="85"/>
+      <c r="A39" s="85" t="s">
+        <v>41</v>
+      </c>
       <c r="B39" s="86"/>
       <c r="C39" s="87"/>
       <c r="D39" s="88"/>
@@ -6090,6 +6180,18 @@
   </sheetData>
   <sheetProtection password="DF87" sheet="1" insertRows="0"/>
   <mergeCells count="28">
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="AG6:AK6"/>
+    <mergeCell ref="AL6:AP6"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
     <mergeCell ref="BU6:BY6"/>
     <mergeCell ref="BZ6:CD6"/>
     <mergeCell ref="CE6:CI6"/>
@@ -6106,18 +6208,6 @@
     <mergeCell ref="R6:V6"/>
     <mergeCell ref="W6:AA6"/>
     <mergeCell ref="AB6:AF6"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="AG6:AK6"/>
-    <mergeCell ref="AL6:AP6"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:C6"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="G10:G14 F15:G38">
@@ -6213,201 +6303,201 @@
       <c r="G1" s="120"/>
     </row>
     <row r="2" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A2" s="110" t="s">
+      <c r="A2" s="113" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="110"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="110"/>
+      <c r="B2" s="113"/>
+      <c r="C2" s="113"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
     </row>
     <row r="3" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A3" s="110" t="s">
+      <c r="A3" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="110"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="110"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="110"/>
+      <c r="B3" s="113"/>
+      <c r="C3" s="113"/>
+      <c r="D3" s="113"/>
+      <c r="E3" s="113"/>
+      <c r="F3" s="113"/>
+      <c r="G3" s="113"/>
     </row>
     <row r="4" spans="1:92" x14ac:dyDescent="0.45">
-      <c r="A4" s="110" t="s">
+      <c r="A4" s="113" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="110"/>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
+      <c r="B4" s="113"/>
+      <c r="C4" s="113"/>
+      <c r="D4" s="113"/>
+      <c r="E4" s="113"/>
+      <c r="F4" s="113"/>
+      <c r="G4" s="113"/>
     </row>
     <row r="5" spans="1:92" ht="18.75" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D5" s="114"/>
-      <c r="E5" s="114"/>
-      <c r="F5" s="115"/>
-      <c r="G5" s="115"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="118"/>
     </row>
     <row r="6" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A6" s="80"/>
-      <c r="B6" s="116"/>
-      <c r="C6" s="116"/>
-      <c r="D6" s="111"/>
-      <c r="E6" s="111"/>
-      <c r="F6" s="112"/>
-      <c r="G6" s="113"/>
-      <c r="H6" s="109">
+      <c r="B6" s="119"/>
+      <c r="C6" s="119"/>
+      <c r="D6" s="114"/>
+      <c r="E6" s="114"/>
+      <c r="F6" s="115"/>
+      <c r="G6" s="116"/>
+      <c r="H6" s="108">
         <f>H7</f>
         <v>45761</v>
       </c>
-      <c r="I6" s="109"/>
-      <c r="J6" s="109"/>
-      <c r="K6" s="109"/>
-      <c r="L6" s="109"/>
-      <c r="M6" s="109">
+      <c r="I6" s="108"/>
+      <c r="J6" s="108"/>
+      <c r="K6" s="108"/>
+      <c r="L6" s="108"/>
+      <c r="M6" s="108">
         <f>H6+7</f>
         <v>45768</v>
       </c>
-      <c r="N6" s="109"/>
-      <c r="O6" s="109"/>
-      <c r="P6" s="109"/>
-      <c r="Q6" s="109"/>
-      <c r="R6" s="109">
+      <c r="N6" s="108"/>
+      <c r="O6" s="108"/>
+      <c r="P6" s="108"/>
+      <c r="Q6" s="108"/>
+      <c r="R6" s="108">
         <f>M6+7</f>
         <v>45775</v>
       </c>
-      <c r="S6" s="109"/>
-      <c r="T6" s="109"/>
-      <c r="U6" s="109"/>
-      <c r="V6" s="109"/>
-      <c r="W6" s="109">
+      <c r="S6" s="108"/>
+      <c r="T6" s="108"/>
+      <c r="U6" s="108"/>
+      <c r="V6" s="108"/>
+      <c r="W6" s="108">
         <f>R6+7</f>
         <v>45782</v>
       </c>
-      <c r="X6" s="109"/>
-      <c r="Y6" s="109"/>
-      <c r="Z6" s="109"/>
-      <c r="AA6" s="109"/>
-      <c r="AB6" s="109">
+      <c r="X6" s="108"/>
+      <c r="Y6" s="108"/>
+      <c r="Z6" s="108"/>
+      <c r="AA6" s="108"/>
+      <c r="AB6" s="108">
         <f>W6+7</f>
         <v>45789</v>
       </c>
-      <c r="AC6" s="109"/>
-      <c r="AD6" s="109"/>
-      <c r="AE6" s="109"/>
-      <c r="AF6" s="109"/>
-      <c r="AG6" s="109">
+      <c r="AC6" s="108"/>
+      <c r="AD6" s="108"/>
+      <c r="AE6" s="108"/>
+      <c r="AF6" s="108"/>
+      <c r="AG6" s="108">
         <f>AB6+7</f>
         <v>45796</v>
       </c>
-      <c r="AH6" s="109"/>
-      <c r="AI6" s="109"/>
-      <c r="AJ6" s="109"/>
-      <c r="AK6" s="109"/>
-      <c r="AL6" s="109">
+      <c r="AH6" s="108"/>
+      <c r="AI6" s="108"/>
+      <c r="AJ6" s="108"/>
+      <c r="AK6" s="108"/>
+      <c r="AL6" s="108">
         <f>AG6+7</f>
         <v>45803</v>
       </c>
-      <c r="AM6" s="109"/>
-      <c r="AN6" s="109"/>
-      <c r="AO6" s="109"/>
-      <c r="AP6" s="109"/>
-      <c r="AQ6" s="109">
+      <c r="AM6" s="108"/>
+      <c r="AN6" s="108"/>
+      <c r="AO6" s="108"/>
+      <c r="AP6" s="108"/>
+      <c r="AQ6" s="108">
         <f>AL6+7</f>
         <v>45810</v>
       </c>
-      <c r="AR6" s="109"/>
-      <c r="AS6" s="109"/>
-      <c r="AT6" s="109"/>
-      <c r="AU6" s="109"/>
-      <c r="AV6" s="109">
+      <c r="AR6" s="108"/>
+      <c r="AS6" s="108"/>
+      <c r="AT6" s="108"/>
+      <c r="AU6" s="108"/>
+      <c r="AV6" s="108">
         <f>AQ6+7</f>
         <v>45817</v>
       </c>
-      <c r="AW6" s="109"/>
-      <c r="AX6" s="109"/>
-      <c r="AY6" s="109"/>
-      <c r="AZ6" s="109"/>
-      <c r="BA6" s="109">
+      <c r="AW6" s="108"/>
+      <c r="AX6" s="108"/>
+      <c r="AY6" s="108"/>
+      <c r="AZ6" s="108"/>
+      <c r="BA6" s="108">
         <f>AV6+7</f>
         <v>45824</v>
       </c>
-      <c r="BB6" s="109"/>
-      <c r="BC6" s="109"/>
-      <c r="BD6" s="109"/>
-      <c r="BE6" s="109"/>
-      <c r="BF6" s="109">
+      <c r="BB6" s="108"/>
+      <c r="BC6" s="108"/>
+      <c r="BD6" s="108"/>
+      <c r="BE6" s="108"/>
+      <c r="BF6" s="108">
         <f>BA6+7</f>
         <v>45831</v>
       </c>
-      <c r="BG6" s="109"/>
-      <c r="BH6" s="109"/>
-      <c r="BI6" s="109"/>
-      <c r="BJ6" s="109"/>
-      <c r="BK6" s="109">
+      <c r="BG6" s="108"/>
+      <c r="BH6" s="108"/>
+      <c r="BI6" s="108"/>
+      <c r="BJ6" s="108"/>
+      <c r="BK6" s="108">
         <f>BF6+7</f>
         <v>45838</v>
       </c>
-      <c r="BL6" s="109"/>
-      <c r="BM6" s="109"/>
-      <c r="BN6" s="109"/>
-      <c r="BO6" s="109"/>
-      <c r="BP6" s="109">
+      <c r="BL6" s="108"/>
+      <c r="BM6" s="108"/>
+      <c r="BN6" s="108"/>
+      <c r="BO6" s="108"/>
+      <c r="BP6" s="108">
         <f>BK6+7</f>
         <v>45845</v>
       </c>
-      <c r="BQ6" s="109"/>
-      <c r="BR6" s="109"/>
-      <c r="BS6" s="109"/>
-      <c r="BT6" s="109"/>
-      <c r="BU6" s="109">
+      <c r="BQ6" s="108"/>
+      <c r="BR6" s="108"/>
+      <c r="BS6" s="108"/>
+      <c r="BT6" s="108"/>
+      <c r="BU6" s="108">
         <f>BP6+7</f>
         <v>45852</v>
       </c>
-      <c r="BV6" s="109"/>
-      <c r="BW6" s="109"/>
-      <c r="BX6" s="109"/>
-      <c r="BY6" s="109"/>
-      <c r="BZ6" s="109">
+      <c r="BV6" s="108"/>
+      <c r="BW6" s="108"/>
+      <c r="BX6" s="108"/>
+      <c r="BY6" s="108"/>
+      <c r="BZ6" s="108">
         <f>BU6+7</f>
         <v>45859</v>
       </c>
-      <c r="CA6" s="109"/>
-      <c r="CB6" s="109"/>
-      <c r="CC6" s="109"/>
-      <c r="CD6" s="109"/>
-      <c r="CE6" s="109">
+      <c r="CA6" s="108"/>
+      <c r="CB6" s="108"/>
+      <c r="CC6" s="108"/>
+      <c r="CD6" s="108"/>
+      <c r="CE6" s="108">
         <f>BZ6+7</f>
         <v>45866</v>
       </c>
-      <c r="CF6" s="109"/>
-      <c r="CG6" s="109"/>
-      <c r="CH6" s="109"/>
-      <c r="CI6" s="109"/>
-      <c r="CJ6" s="109">
+      <c r="CF6" s="108"/>
+      <c r="CG6" s="108"/>
+      <c r="CH6" s="108"/>
+      <c r="CI6" s="108"/>
+      <c r="CJ6" s="108">
         <f>CE6+7</f>
         <v>45873</v>
       </c>
-      <c r="CK6" s="109"/>
-      <c r="CL6" s="109"/>
-      <c r="CM6" s="109"/>
-      <c r="CN6" s="109"/>
+      <c r="CK6" s="108"/>
+      <c r="CL6" s="108"/>
+      <c r="CM6" s="108"/>
+      <c r="CN6" s="108"/>
     </row>
     <row r="7" spans="1:92" x14ac:dyDescent="0.45">
       <c r="A7" s="75"/>
       <c r="B7" s="75"/>
       <c r="C7" s="76"/>
-      <c r="D7" s="117" t="s">
+      <c r="D7" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="E7" s="118"/>
-      <c r="F7" s="119" t="s">
+      <c r="E7" s="110"/>
+      <c r="F7" s="111" t="s">
         <v>3</v>
       </c>
-      <c r="G7" s="118"/>
+      <c r="G7" s="110"/>
       <c r="H7" s="77">
         <f>E1-WEEKDAY(E1,1)+2</f>
         <v>45761</v>
@@ -9491,18 +9581,6 @@
   </sheetData>
   <sheetProtection insertRows="0"/>
   <mergeCells count="28">
-    <mergeCell ref="R6:V6"/>
-    <mergeCell ref="E1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="M6:Q6"/>
     <mergeCell ref="CE6:CI6"/>
     <mergeCell ref="CJ6:CN6"/>
     <mergeCell ref="D7:E7"/>
@@ -9519,6 +9597,18 @@
     <mergeCell ref="AL6:AP6"/>
     <mergeCell ref="AQ6:AU6"/>
     <mergeCell ref="AV6:AZ6"/>
+    <mergeCell ref="R6:V6"/>
+    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="M6:Q6"/>
   </mergeCells>
   <phoneticPr fontId="19"/>
   <conditionalFormatting sqref="F15:G32">
@@ -9552,33 +9642,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <SharedWithUsers xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </SharedWithUsers>
-    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100A6A6C361903FA540AF4D79E6EA2B777C" ma:contentTypeVersion="18" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="ea7c12cc56e366ff4dda5c6e96eadaab">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="aaa52e1c-8772-4366-aa63-bf636c80ebd4" xmlns:ns3="0c73c1f5-50cd-4477-a315-44bef7b8a847" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7966d967ae6f075ad6e4da9e3740ee6a" ns2:_="" ns3:_="">
     <xsd:import namespace="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
@@ -9833,10 +9896,48 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <SharedWithUsers xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </SharedWithUsers>
+    <TaxCatchAll xmlns="0c73c1f5-50cd-4477-a315-44bef7b8a847" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="aaa52e1c-8772-4366-aa63-bf636c80ebd4">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C6FCD32-0857-4D4D-96CB-BC4A6CBBBA17}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
+    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9853,20 +9954,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C6FCD32-0857-4D4D-96CB-BC4A6CBBBA17}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4A34E49-7289-4AEA-9593-4F55E04ADB10}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="aaa52e1c-8772-4366-aa63-bf636c80ebd4"/>
-    <ds:schemaRef ds:uri="0c73c1f5-50cd-4477-a315-44bef7b8a847"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>